--- a/005_品質マネジメント/テスト分析マトリクス.xlsx
+++ b/005_品質マネジメント/テスト分析マトリクス.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanakahda/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanakahda/Desktop/project-management-toolbox/005_品質マネジメント/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFACB59-22D9-F74A-9520-5B8AC8AD44BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB41425-93DF-794A-9D9F-3FC0D065E698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="28300" windowHeight="16900" activeTab="1" xr2:uid="{4AE127D2-DEF3-DF4A-AD27-233C72195F1B}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="28300" windowHeight="16900" xr2:uid="{4AE127D2-DEF3-DF4A-AD27-233C72195F1B}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -590,99 +590,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{449CDBBC-D996-859B-E81F-E38D405FB2C9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="355600" y="254000"/>
-          <a:ext cx="6299200" cy="5854700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B77D5201-6802-CA45-9FC0-184C08C3BC0A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6870700" y="393700"/>
-          <a:ext cx="5880100" cy="4787900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -987,7 +894,6 @@
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
